--- a/data/nzd0336/nzd0336.xlsx
+++ b/data/nzd0336/nzd0336.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K468"/>
+  <dimension ref="A1:K471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18612,11 +18612,11 @@
     <row r="467">
       <c r="A467" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17 22:12:23+00:00</t>
+          <t>2026-06-24 22:18:38+00:00</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>384.33</v>
+        <v>377.14</v>
       </c>
       <c r="C467" t="n">
         <v>374.77</v>
@@ -18628,16 +18628,16 @@
         <v>369.62</v>
       </c>
       <c r="F467" t="n">
-        <v>367.63</v>
+        <v>362.42</v>
       </c>
       <c r="G467" t="n">
-        <v>361.2</v>
+        <v>355.72</v>
       </c>
       <c r="H467" t="n">
-        <v>352.7</v>
+        <v>350.97</v>
       </c>
       <c r="I467" t="n">
-        <v>346.29</v>
+        <v>344.23</v>
       </c>
       <c r="J467" t="n">
         <v>353.34</v>
@@ -18651,37 +18651,154 @@
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24 22:18:38+00:00</t>
+          <t>2026-07-10 22:18:43+00:00</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>384.33</v>
+        <v>376.26</v>
       </c>
       <c r="C468" t="n">
-        <v>374.77</v>
+        <v>373.22</v>
       </c>
       <c r="D468" t="n">
-        <v>375.09</v>
+        <v>373.73</v>
       </c>
       <c r="E468" t="n">
-        <v>369.62</v>
+        <v>369.55</v>
       </c>
       <c r="F468" t="n">
-        <v>367.63</v>
+        <v>362.54</v>
       </c>
       <c r="G468" t="n">
-        <v>361.2</v>
+        <v>356.17</v>
       </c>
       <c r="H468" t="n">
-        <v>350.97</v>
+        <v>351.74</v>
       </c>
       <c r="I468" t="n">
-        <v>344.23</v>
+        <v>344.04</v>
       </c>
       <c r="J468" t="n">
-        <v>348.87</v>
+        <v>353.11</v>
       </c>
       <c r="K468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:18:39+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>376.26</v>
+      </c>
+      <c r="C469" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="D469" t="n">
+        <v>372.98</v>
+      </c>
+      <c r="E469" t="n">
+        <v>368.74</v>
+      </c>
+      <c r="F469" t="n">
+        <v>361.83</v>
+      </c>
+      <c r="G469" t="n">
+        <v>355.35</v>
+      </c>
+      <c r="H469" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="I469" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="J469" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>375.57</v>
+      </c>
+      <c r="C470" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="D470" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="E470" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="F470" t="n">
+        <v>361.8</v>
+      </c>
+      <c r="G470" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="H470" t="n">
+        <v>351.98</v>
+      </c>
+      <c r="I470" t="n">
+        <v>344.22</v>
+      </c>
+      <c r="J470" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>375.57</v>
+      </c>
+      <c r="C471" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="D471" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="E471" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="F471" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="G471" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="H471" t="n">
+        <v>351.98</v>
+      </c>
+      <c r="I471" t="n">
+        <v>344.22</v>
+      </c>
+      <c r="J471" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="K471" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18698,7 +18815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B539"/>
+  <dimension ref="A1:B544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24091,6 +24208,56 @@
       </c>
       <c r="B539" t="n">
         <v>-0.2</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -24259,28 +24426,28 @@
         <v>0.0861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3313215657744775</v>
+        <v>0.3239264932570914</v>
       </c>
       <c r="J2" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K2" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07039815327762189</v>
+        <v>0.06846516530418334</v>
       </c>
       <c r="M2" t="n">
-        <v>7.01658143875147</v>
+        <v>6.955300562221912</v>
       </c>
       <c r="N2" t="n">
-        <v>87.69858267864041</v>
+        <v>86.92947829550745</v>
       </c>
       <c r="O2" t="n">
-        <v>9.364752141869021</v>
+        <v>9.323597926525331</v>
       </c>
       <c r="P2" t="n">
-        <v>368.2597754672477</v>
+        <v>368.336501159056</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24337,28 +24504,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.423149672274642</v>
+        <v>0.4241707115010994</v>
       </c>
       <c r="J3" t="n">
+        <v>470</v>
+      </c>
+      <c r="K3" t="n">
         <v>467</v>
       </c>
-      <c r="K3" t="n">
-        <v>464</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1245236151597341</v>
+        <v>0.1264892245039645</v>
       </c>
       <c r="M3" t="n">
-        <v>6.67076756588593</v>
+        <v>6.632623109862705</v>
       </c>
       <c r="N3" t="n">
-        <v>74.73424114703313</v>
+        <v>74.24122555505434</v>
       </c>
       <c r="O3" t="n">
-        <v>8.644896826858787</v>
+        <v>8.616334809828036</v>
       </c>
       <c r="P3" t="n">
-        <v>358.8035783476442</v>
+        <v>358.7927303472404</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24415,28 +24582,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2375366394672186</v>
+        <v>0.2366567174941186</v>
       </c>
       <c r="J4" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K4" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03437446780391185</v>
+        <v>0.03455935339552241</v>
       </c>
       <c r="M4" t="n">
-        <v>6.072146628032876</v>
+        <v>6.031294528632039</v>
       </c>
       <c r="N4" t="n">
-        <v>94.58047403572331</v>
+        <v>93.96625662551278</v>
       </c>
       <c r="O4" t="n">
-        <v>9.725249304553756</v>
+        <v>9.693619376967138</v>
       </c>
       <c r="P4" t="n">
-        <v>366.5285195900095</v>
+        <v>366.5377393774069</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24493,28 +24660,28 @@
         <v>0.0964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1675523160497347</v>
+        <v>0.1761789971912112</v>
       </c>
       <c r="J5" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K5" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02814502304186872</v>
+        <v>0.03123067925505396</v>
       </c>
       <c r="M5" t="n">
-        <v>5.758136138222714</v>
+        <v>5.772511110526209</v>
       </c>
       <c r="N5" t="n">
-        <v>58.71325081200521</v>
+        <v>58.68916909010523</v>
       </c>
       <c r="O5" t="n">
-        <v>7.662457230680325</v>
+        <v>7.66088565964179</v>
       </c>
       <c r="P5" t="n">
-        <v>356.4913552339289</v>
+        <v>356.40147101009</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24571,28 +24738,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5944202811638896</v>
+        <v>0.6011473427261135</v>
       </c>
       <c r="J6" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K6" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3538236587408923</v>
+        <v>0.3618237590072148</v>
       </c>
       <c r="M6" t="n">
-        <v>4.868337734797033</v>
+        <v>4.874999733763424</v>
       </c>
       <c r="N6" t="n">
-        <v>39.03991602458667</v>
+        <v>38.8105778654221</v>
       </c>
       <c r="O6" t="n">
-        <v>6.248193020753014</v>
+        <v>6.229813630071296</v>
       </c>
       <c r="P6" t="n">
-        <v>337.1234861916012</v>
+        <v>337.0531889970997</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24649,28 +24816,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4752815503956202</v>
+        <v>0.4773635079784848</v>
       </c>
       <c r="J7" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K7" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2397911950195821</v>
+        <v>0.244619373713533</v>
       </c>
       <c r="M7" t="n">
-        <v>4.817862997536927</v>
+        <v>4.799936245395721</v>
       </c>
       <c r="N7" t="n">
-        <v>43.32704087248849</v>
+        <v>42.84677314401652</v>
       </c>
       <c r="O7" t="n">
-        <v>6.582327921980831</v>
+        <v>6.545744659243631</v>
       </c>
       <c r="P7" t="n">
-        <v>337.2955605653685</v>
+        <v>337.2736486349386</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24727,28 +24894,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6669626113519577</v>
+        <v>0.6697777538463772</v>
       </c>
       <c r="J8" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K8" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1824732836168476</v>
+        <v>0.1856196530310105</v>
       </c>
       <c r="M8" t="n">
-        <v>7.5838106992539</v>
+        <v>7.554872928861889</v>
       </c>
       <c r="N8" t="n">
-        <v>120.5766178690548</v>
+        <v>119.8421138342332</v>
       </c>
       <c r="O8" t="n">
-        <v>10.98073849379243</v>
+        <v>10.94724229357482</v>
       </c>
       <c r="P8" t="n">
-        <v>331.1729391462433</v>
+        <v>331.1435906695907</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24805,28 +24972,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7404461205835369</v>
+        <v>0.7348495960934789</v>
       </c>
       <c r="J9" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K9" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L9" t="n">
-        <v>0.208222847825334</v>
+        <v>0.2076566260075005</v>
       </c>
       <c r="M9" t="n">
-        <v>7.860383941817207</v>
+        <v>7.823844212193444</v>
       </c>
       <c r="N9" t="n">
-        <v>126.1301641460943</v>
+        <v>125.4611465524183</v>
       </c>
       <c r="O9" t="n">
-        <v>11.23076863558743</v>
+        <v>11.20094400273559</v>
       </c>
       <c r="P9" t="n">
-        <v>328.4946829631186</v>
+        <v>328.5529399342006</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24883,28 +25050,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3827324047134065</v>
+        <v>0.3950620115104762</v>
       </c>
       <c r="J10" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K10" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08796637774583116</v>
+        <v>0.09363340496160077</v>
       </c>
       <c r="M10" t="n">
-        <v>6.82327460491657</v>
+        <v>6.84966741615298</v>
       </c>
       <c r="N10" t="n">
-        <v>92.03506470923595</v>
+        <v>92.14000634251259</v>
       </c>
       <c r="O10" t="n">
-        <v>9.59349074681557</v>
+        <v>9.598958607188209</v>
       </c>
       <c r="P10" t="n">
-        <v>332.2541198568896</v>
+        <v>332.1257947206665</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24942,7 +25109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K468"/>
+  <dimension ref="A1:K471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51482,12 +51649,12 @@
     <row r="467">
       <c r="A467" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17 22:12:23+00:00</t>
+          <t>2026-06-24 22:18:38+00:00</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>-41.05101136754979,172.1068296355765</t>
+          <t>-41.05100291474932,172.10691445573744</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -51507,22 +51674,22 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>-41.048307615298484,172.10653286996427</t>
+          <t>-41.04830149030424,172.1065943296308</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>-41.047629009206645,172.1064852768573</t>
+          <t>-41.04762256679072,172.10654992090838</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>-41.04694796277821,172.10646210042034</t>
+          <t>-41.04694592894858,172.10648250791255</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>-41.04626936659875,172.1064142680506</t>
+          <t>-41.04626694481182,172.1064385680513</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -51539,55 +51706,226 @@
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24 22:18:38+00:00</t>
+          <t>2026-07-10 22:18:43+00:00</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>-41.05101136754979,172.1068296355765</t>
+          <t>-41.051001880188075,172.10692483706313</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>-41.05032910892725,172.1068189716693</t>
+          <t>-41.05032728669494,172.10683725677296</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>-41.049658458725446,172.10669175385263</t>
+          <t>-41.04965685987418,172.10670779739516</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>-41.04898099483021,172.1066328384422</t>
+          <t>-41.04898091253647,172.1066336642043</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>-41.048307615298484,172.10653286996427</t>
+          <t>-41.048301631379324,172.10659291405318</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>-41.047629009206645,172.1064852768573</t>
+          <t>-41.04762309582259,172.10654461254697</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>-41.04694592894858,172.10648250791255</t>
+          <t>-41.04694683417955,172.10647342480922</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>-41.04626694481182,172.1064385680513</t>
+          <t>-41.04626672144285,172.1064408093134</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>-41.04560133243003,172.10626038812183</t>
+          <t>-41.04560631701844,172.1062103730804</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:18:39+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>-41.051001880188075,172.10692483706313</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>-41.05032587593244,172.10685141298163</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-41.04965597815377,172.10671664493668</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-41.04897996028022,172.10664321945157</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-41.04830079668478,172.10660128955396</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>-41.047622131808765,172.10655428556103</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>-41.0469468459358,172.10647330684685</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-41.04626733276833,172.10643467533285</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>-41.045605599897385,172.10621756864106</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-41.05100106899736,172.10693297696596</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-41.05032511176869,172.1068590809277</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-41.049655343314654,172.1067230151664</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-41.048979572323745,172.10664711233</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-41.04830076141598,172.10660164344836</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-41.04762219059012,172.10655369574312</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-41.04694711632933,172.10647059371206</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-41.04626693305555,172.10643868601247</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-41.04560449482474,172.10622865688177</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-41.05100106899736,172.10693297696596</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-41.05032511176869,172.1068590809277</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-41.049655343314654,172.1067230151664</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-41.048979572323745,172.10664711233</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-41.0483027717357,172.10658147146728</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-41.04762219059012,172.10655369574312</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>-41.04694711632933,172.10647059371206</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-41.04626693305555,172.10643868601247</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>-41.04560449482474,172.10622865688177</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0336/nzd0336.xlsx
+++ b/data/nzd0336/nzd0336.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K471"/>
+  <dimension ref="A1:K474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18801,6 +18801,123 @@
       <c r="K471" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:18:49+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="C472" t="n">
+        <v>369.08</v>
+      </c>
+      <c r="D472" t="n">
+        <v>370.31</v>
+      </c>
+      <c r="E472" t="n">
+        <v>367.88</v>
+      </c>
+      <c r="F472" t="n">
+        <v>365.21</v>
+      </c>
+      <c r="G472" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="H472" t="n">
+        <v>351.99</v>
+      </c>
+      <c r="I472" t="n">
+        <v>344.33</v>
+      </c>
+      <c r="J472" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="C473" t="n">
+        <v>367.47</v>
+      </c>
+      <c r="D473" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="E473" t="n">
+        <v>368.19</v>
+      </c>
+      <c r="F473" t="n">
+        <v>365.76</v>
+      </c>
+      <c r="G473" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="H473" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="I473" t="n">
+        <v>344.79</v>
+      </c>
+      <c r="J473" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>371.26</v>
+      </c>
+      <c r="C474" t="n">
+        <v>367.27</v>
+      </c>
+      <c r="D474" t="n">
+        <v>372.2</v>
+      </c>
+      <c r="E474" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="F474" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="G474" t="n">
+        <v>357.86</v>
+      </c>
+      <c r="H474" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="I474" t="n">
+        <v>345.56</v>
+      </c>
+      <c r="J474" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18815,7 +18932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B544"/>
+  <dimension ref="A1:B547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24258,6 +24375,36 @@
       </c>
       <c r="B544" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -24426,28 +24573,28 @@
         <v>0.0861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3239264932570914</v>
+        <v>0.3172029318979384</v>
       </c>
       <c r="J2" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06846516530418334</v>
+        <v>0.06645754719546426</v>
       </c>
       <c r="M2" t="n">
-        <v>6.955300562221912</v>
+        <v>6.951514836349346</v>
       </c>
       <c r="N2" t="n">
-        <v>86.92947829550745</v>
+        <v>86.5971792474802</v>
       </c>
       <c r="O2" t="n">
-        <v>9.323597926525331</v>
+        <v>9.305760541056287</v>
       </c>
       <c r="P2" t="n">
-        <v>368.336501159056</v>
+        <v>368.4066472207464</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24504,28 +24651,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4241707115010994</v>
+        <v>0.4215254929433513</v>
       </c>
       <c r="J3" t="n">
+        <v>473</v>
+      </c>
+      <c r="K3" t="n">
         <v>470</v>
       </c>
-      <c r="K3" t="n">
-        <v>467</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1264892245039645</v>
+        <v>0.1264496843430991</v>
       </c>
       <c r="M3" t="n">
-        <v>6.632623109862705</v>
+        <v>6.60688368645836</v>
       </c>
       <c r="N3" t="n">
-        <v>74.24122555505434</v>
+        <v>73.80460278015067</v>
       </c>
       <c r="O3" t="n">
-        <v>8.616334809828036</v>
+        <v>8.590960527214095</v>
       </c>
       <c r="P3" t="n">
-        <v>358.7927303472404</v>
+        <v>358.8207388271422</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24582,28 +24729,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2366567174941186</v>
+        <v>0.2346933112753719</v>
       </c>
       <c r="J4" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K4" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03455935339552241</v>
+        <v>0.0344174498426344</v>
       </c>
       <c r="M4" t="n">
-        <v>6.031294528632039</v>
+        <v>6.00116218442317</v>
       </c>
       <c r="N4" t="n">
-        <v>93.96625662551278</v>
+        <v>93.38989452467446</v>
       </c>
       <c r="O4" t="n">
-        <v>9.693619376967138</v>
+        <v>9.663844707189497</v>
       </c>
       <c r="P4" t="n">
-        <v>366.5377393774069</v>
+        <v>366.5584305530351</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24660,28 +24807,28 @@
         <v>0.0964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1761789971912112</v>
+        <v>0.1843294290531912</v>
       </c>
       <c r="J5" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K5" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03123067925505396</v>
+        <v>0.0343181887525067</v>
       </c>
       <c r="M5" t="n">
-        <v>5.772511110526209</v>
+        <v>5.784448179242184</v>
       </c>
       <c r="N5" t="n">
-        <v>58.68916909010523</v>
+        <v>58.63986344565987</v>
       </c>
       <c r="O5" t="n">
-        <v>7.66088565964179</v>
+        <v>7.657666971451545</v>
       </c>
       <c r="P5" t="n">
-        <v>356.40147101009</v>
+        <v>356.3164332458925</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24738,28 +24885,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6011473427261135</v>
+        <v>0.6152408429898152</v>
       </c>
       <c r="J6" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3618237590072148</v>
+        <v>0.3697691181614832</v>
       </c>
       <c r="M6" t="n">
-        <v>4.874999733763424</v>
+        <v>4.925715913138147</v>
       </c>
       <c r="N6" t="n">
-        <v>38.8105778654221</v>
+        <v>39.52746438033143</v>
       </c>
       <c r="O6" t="n">
-        <v>6.229813630071296</v>
+        <v>6.28708711410391</v>
       </c>
       <c r="P6" t="n">
-        <v>337.0531889970997</v>
+        <v>336.9061477678814</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24816,28 +24963,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4773635079784848</v>
+        <v>0.4852853106204244</v>
       </c>
       <c r="J7" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K7" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L7" t="n">
-        <v>0.244619373713533</v>
+        <v>0.2517675425105339</v>
       </c>
       <c r="M7" t="n">
-        <v>4.799936245395721</v>
+        <v>4.818733220107692</v>
       </c>
       <c r="N7" t="n">
-        <v>42.84677314401652</v>
+        <v>42.88157124673447</v>
       </c>
       <c r="O7" t="n">
-        <v>6.545744659243631</v>
+        <v>6.548402190361743</v>
       </c>
       <c r="P7" t="n">
-        <v>337.2736486349386</v>
+        <v>337.1909943695609</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24894,28 +25041,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6697777538463772</v>
+        <v>0.6738941063898323</v>
       </c>
       <c r="J8" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K8" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1856196530310105</v>
+        <v>0.1892906857393848</v>
       </c>
       <c r="M8" t="n">
-        <v>7.554872928861889</v>
+        <v>7.535198558414881</v>
       </c>
       <c r="N8" t="n">
-        <v>119.8421138342332</v>
+        <v>119.1677750613248</v>
       </c>
       <c r="O8" t="n">
-        <v>10.94724229357482</v>
+        <v>10.91639936340388</v>
       </c>
       <c r="P8" t="n">
-        <v>331.1435906695907</v>
+        <v>331.1006362519236</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24972,28 +25119,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7348495960934789</v>
+        <v>0.7308972046876324</v>
       </c>
       <c r="J9" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K9" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2076566260075005</v>
+        <v>0.2078479449533908</v>
       </c>
       <c r="M9" t="n">
-        <v>7.823844212193444</v>
+        <v>7.78398158868879</v>
       </c>
       <c r="N9" t="n">
-        <v>125.4611465524183</v>
+        <v>124.7426645464157</v>
       </c>
       <c r="O9" t="n">
-        <v>11.20094400273559</v>
+        <v>11.16882556701535</v>
       </c>
       <c r="P9" t="n">
-        <v>328.5529399342006</v>
+        <v>328.5941698672487</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25050,28 +25197,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3950620115104762</v>
+        <v>0.4041640428863092</v>
       </c>
       <c r="J10" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K10" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09363340496160077</v>
+        <v>0.09829316244472996</v>
       </c>
       <c r="M10" t="n">
-        <v>6.84966741615298</v>
+        <v>6.858105145544069</v>
       </c>
       <c r="N10" t="n">
-        <v>92.14000634251259</v>
+        <v>91.95719472144444</v>
       </c>
       <c r="O10" t="n">
-        <v>9.598958607188209</v>
+        <v>9.589431407619768</v>
       </c>
       <c r="P10" t="n">
-        <v>332.1257947206665</v>
+        <v>332.0308797345859</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25109,7 +25256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K471"/>
+  <dimension ref="A1:K474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51931,6 +52078,177 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:18:49+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-41.050995790365334,172.10698594531468</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-41.05032241955694,172.10688609569036</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-41.04965283922357,172.10674814218265</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-41.04897894924184,172.10665336452863</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-41.04830477029565,172.10656141744988</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>-41.04762322514146,172.10654331494752</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-41.046947128085556,172.10647047574966</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>-41.0462670623744,172.10643738843964</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>-41.045603660141474,172.10623703204206</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-41.050995790365334,172.10698594531468</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-41.05032052677544,172.10690508860083</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-41.049653779727905,172.10673870480585</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-41.04897931368602,172.10664970758225</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-41.04830541688782,172.10655492938517</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-41.047624400766836,172.10653151858847</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-41.04694792750953,172.10646245430752</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-41.04626760316217,172.10643196222603</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>-41.045603954044104,172.10623408304195</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-41.050996001981346,172.10698382186212</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-41.05032029164707,172.10690744796852</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-41.04965506116381,172.1067258463796</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-41.048980218917805,172.10664062419926</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-41.04830586362402,172.10655044672222</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>-41.04762508262899,172.10652467670008</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-41.04694933825632,172.10644829882094</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-41.04626850839329,172.10642287921607</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>-41.04560324867768,172.10624116064213</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
